--- a/Daily_Report/Top 7 broker List with its Turnover 2024-08-14.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-08-14.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="274">
   <si>
     <t>Date: 2024-08-14</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
+    <t>Naasa Securities Co. Ltd.</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
     <t>ABC Securities Pvt. Limited</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
-  </si>
-  <si>
-    <t>Kohinoor Investment and Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Dakshinkali Investment Securities Pvt.Limited</t>
-  </si>
-  <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
-    <t>Midas Stock Broking Company Pvt. Limited</t>
-  </si>
-  <si>
-    <t>Linch Stock Market Limited</t>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>57</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>5,488,867,230.72</t>
-  </si>
-  <si>
-    <t>3,141,780,150.6</t>
-  </si>
-  <si>
-    <t>2,753,048,353.68</t>
-  </si>
-  <si>
-    <t>2,677,847,203.1</t>
-  </si>
-  <si>
-    <t>1,753,746,862.32</t>
-  </si>
-  <si>
-    <t>1,678,429,755.6</t>
-  </si>
-  <si>
-    <t>1,603,611,806.7</t>
-  </si>
-  <si>
-    <t>5,245,147,892.5</t>
-  </si>
-  <si>
-    <t>1,603,727,784.3</t>
-  </si>
-  <si>
-    <t>345,454,228.4</t>
-  </si>
-  <si>
-    <t>2,475,954,617.69</t>
-  </si>
-  <si>
-    <t>768,658,259.67</t>
-  </si>
-  <si>
-    <t>1,448,235,167.4</t>
-  </si>
-  <si>
-    <t>290,431,500.3</t>
-  </si>
-  <si>
-    <t>243,719,338.22</t>
-  </si>
-  <si>
-    <t>1,538,052,366.3</t>
-  </si>
-  <si>
-    <t>2,407,594,125.28</t>
-  </si>
-  <si>
-    <t>201,892,585.4</t>
-  </si>
-  <si>
-    <t>985,088,602.65</t>
-  </si>
-  <si>
-    <t>230,194,588.2</t>
-  </si>
-  <si>
-    <t>1,313,180,306.4</t>
+    <t>34</t>
+  </si>
+  <si>
+    <t>3,287,082,434.2</t>
+  </si>
+  <si>
+    <t>2,159,196,357.3</t>
+  </si>
+  <si>
+    <t>1,502,330,154.2</t>
+  </si>
+  <si>
+    <t>1,391,737,384.9</t>
+  </si>
+  <si>
+    <t>1,381,070,164.21</t>
+  </si>
+  <si>
+    <t>1,217,547,281.82</t>
+  </si>
+  <si>
+    <t>1,168,654,608.66</t>
+  </si>
+  <si>
+    <t>1,423,949,594.2</t>
+  </si>
+  <si>
+    <t>1,489,262,522.5</t>
+  </si>
+  <si>
+    <t>584,982,599.1</t>
+  </si>
+  <si>
+    <t>649,176,660.7</t>
+  </si>
+  <si>
+    <t>621,031,896.4</t>
+  </si>
+  <si>
+    <t>625,400,047.47</t>
+  </si>
+  <si>
+    <t>504,156,829.66</t>
+  </si>
+  <si>
+    <t>1,863,132,840.0</t>
+  </si>
+  <si>
+    <t>669,933,834.79</t>
+  </si>
+  <si>
+    <t>917,347,555.1</t>
+  </si>
+  <si>
+    <t>742,560,724.2</t>
+  </si>
+  <si>
+    <t>760,038,267.82</t>
+  </si>
+  <si>
+    <t>592,147,234.35</t>
+  </si>
+  <si>
+    <t>664,497,779.0</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,316 +179,325 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>336,314,411.39</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>119,021,970.3</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>79,044,014.5</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>78,155,160.7</t>
+  </si>
+  <si>
+    <t>SSHL</t>
+  </si>
+  <si>
+    <t>66,251,425.0</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>747,553,230.0</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>153,897,814.3</t>
+  </si>
+  <si>
+    <t>135,347,781.8</t>
+  </si>
+  <si>
+    <t>GLH</t>
+  </si>
+  <si>
+    <t>68,310,583.0</t>
+  </si>
+  <si>
+    <t>UPPER</t>
+  </si>
+  <si>
+    <t>20,882,979.1</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>64,919,649.9</t>
+  </si>
+  <si>
+    <t>48,287,227.9</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>36,171,387.4</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>17,368,567.2</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>15,924,868.6</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>127,985,637.0</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>84,990,331.7</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>34,737,000.0</t>
+  </si>
+  <si>
+    <t>28,865,478.1</t>
+  </si>
+  <si>
+    <t>27,315,835.0</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>191,653,800.0</t>
+  </si>
+  <si>
+    <t>MNBBL</t>
+  </si>
+  <si>
+    <t>29,683,724.2</t>
+  </si>
+  <si>
+    <t>RADHI</t>
+  </si>
+  <si>
+    <t>29,629,250.6</t>
+  </si>
+  <si>
     <t>MFIL</t>
   </si>
   <si>
-    <t>3,389,594,970.8</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>833,937,332.2</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>619,283,724.2</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>42,873,817.2</t>
-  </si>
-  <si>
-    <t>RADHI</t>
-  </si>
-  <si>
-    <t>29,452,951.6</t>
+    <t>23,615,361.8</t>
+  </si>
+  <si>
+    <t>NBL</t>
+  </si>
+  <si>
+    <t>20,493,245.89</t>
+  </si>
+  <si>
+    <t>157,094,594.3</t>
+  </si>
+  <si>
+    <t>56,133,061.4</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>21,972,748.6</t>
+  </si>
+  <si>
+    <t>17,237,475.5</t>
   </si>
   <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>268,757,495.3</t>
-  </si>
-  <si>
-    <t>BFC</t>
-  </si>
-  <si>
-    <t>112,128,086.6</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>85,802,864.5</t>
-  </si>
-  <si>
-    <t>SIFC</t>
-  </si>
-  <si>
-    <t>70,113,385.5</t>
-  </si>
-  <si>
-    <t>AKJCL</t>
-  </si>
-  <si>
-    <t>69,408,182.0</t>
+    <t>14,379,391.6</t>
+  </si>
+  <si>
+    <t>76,102,281.5</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>47,868,456.3</t>
+  </si>
+  <si>
+    <t>NUBL</t>
+  </si>
+  <si>
+    <t>14,586,160.0</t>
+  </si>
+  <si>
+    <t>12,908,326.3</t>
+  </si>
+  <si>
+    <t>12,277,859.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>698,816,332.5</t>
+  </si>
+  <si>
+    <t>MKJC</t>
+  </si>
+  <si>
+    <t>130,288,429.1</t>
+  </si>
+  <si>
+    <t>120,902,279.2</t>
+  </si>
+  <si>
+    <t>112,433,797.4</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>65,374,402.0</t>
+  </si>
+  <si>
+    <t>GBBL</t>
+  </si>
+  <si>
+    <t>89,173,861.3</t>
+  </si>
+  <si>
+    <t>74,614,907.7</t>
+  </si>
+  <si>
+    <t>56,460,188.1</t>
+  </si>
+  <si>
+    <t>BEDC</t>
+  </si>
+  <si>
+    <t>27,668,971.0</t>
+  </si>
+  <si>
+    <t>22,034,292.6</t>
+  </si>
+  <si>
+    <t>BHL</t>
+  </si>
+  <si>
+    <t>125,064,327.0</t>
+  </si>
+  <si>
+    <t>90,929,775.1</t>
+  </si>
+  <si>
+    <t>84,077,917.59</t>
+  </si>
+  <si>
+    <t>59,083,283.5</t>
+  </si>
+  <si>
+    <t>55,381,349.7</t>
+  </si>
+  <si>
+    <t>111,109,413.3</t>
+  </si>
+  <si>
+    <t>MLBL</t>
+  </si>
+  <si>
+    <t>110,095,829.8</t>
+  </si>
+  <si>
+    <t>58,105,665.0</t>
+  </si>
+  <si>
+    <t>41,462,165.0</t>
+  </si>
+  <si>
+    <t>37,086,710.5</t>
+  </si>
+  <si>
+    <t>NTC</t>
+  </si>
+  <si>
+    <t>288,688,725.0</t>
+  </si>
+  <si>
+    <t>HIDCL</t>
+  </si>
+  <si>
+    <t>127,365,546.0</t>
   </si>
   <si>
     <t>SONA</t>
   </si>
   <si>
-    <t>81,703,635.59</t>
-  </si>
-  <si>
-    <t>SMJC</t>
-  </si>
-  <si>
-    <t>32,688,688.0</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>9,874,002.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>9,384,135.0</t>
-  </si>
-  <si>
-    <t>9,327,169.0</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>2,123,889,934.0</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>71,890,250.0</t>
-  </si>
-  <si>
-    <t>NBL</t>
-  </si>
-  <si>
-    <t>39,677,500.0</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>25,762,881.9</t>
-  </si>
-  <si>
-    <t>19,457,760.2</t>
-  </si>
-  <si>
-    <t>245,744,901.6</t>
-  </si>
-  <si>
-    <t>56,073,681.4</t>
-  </si>
-  <si>
-    <t>53,855,493.0</t>
-  </si>
-  <si>
-    <t>30,250,122.2</t>
-  </si>
-  <si>
-    <t>21,548,548.6</t>
-  </si>
-  <si>
-    <t>1,013,079,128.6</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>126,731,280.0</t>
-  </si>
-  <si>
-    <t>MEHL</t>
-  </si>
-  <si>
-    <t>113,429,200.0</t>
-  </si>
-  <si>
-    <t>24,497,932.0</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>19,712,978.1</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>78,477,260.0</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>31,011,037.8</t>
-  </si>
-  <si>
-    <t>22,757,590.0</t>
-  </si>
-  <si>
-    <t>10,910,023.6</t>
-  </si>
-  <si>
-    <t>7,365,620.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>26,224,938.3</t>
-  </si>
-  <si>
-    <t>24,049,465.0</t>
-  </si>
-  <si>
-    <t>11,571,912.3</t>
-  </si>
-  <si>
-    <t>9,395,175.9</t>
-  </si>
-  <si>
-    <t>9,154,465.5</t>
-  </si>
-  <si>
-    <t>655,453,370.5</t>
-  </si>
-  <si>
-    <t>60,223,379.2</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>54,904,541.2</t>
-  </si>
-  <si>
-    <t>49,446,362.4</t>
-  </si>
-  <si>
-    <t>MKJC</t>
-  </si>
-  <si>
-    <t>45,345,861.1</t>
-  </si>
-  <si>
-    <t>2,140,203,810.0</t>
-  </si>
-  <si>
-    <t>34,466,946.0</t>
-  </si>
-  <si>
-    <t>16,374,391.6</t>
-  </si>
-  <si>
-    <t>12,428,506.0</t>
-  </si>
-  <si>
-    <t>12,418,093.3</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>12,069,054.0</t>
-  </si>
-  <si>
-    <t>10,170,244.5</t>
-  </si>
-  <si>
-    <t>SKBBL</t>
-  </si>
-  <si>
-    <t>9,941,706.0</t>
-  </si>
-  <si>
-    <t>CHCL</t>
-  </si>
-  <si>
-    <t>7,761,725.0</t>
-  </si>
-  <si>
-    <t>7,678,662.1</t>
-  </si>
-  <si>
-    <t>184,750,882.8</t>
-  </si>
-  <si>
-    <t>154,876,821.0</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>100,048,984.5</t>
-  </si>
-  <si>
-    <t>48,656,236.5</t>
-  </si>
-  <si>
-    <t>34,167,289.79</t>
-  </si>
-  <si>
-    <t>21,316,116.7</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>15,794,152.4</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>10,839,422.7</t>
-  </si>
-  <si>
-    <t>9,636,541.0</t>
-  </si>
-  <si>
-    <t>8,209,922.7</t>
-  </si>
-  <si>
-    <t>843,314,292.0</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>126,662,541.0</t>
-  </si>
-  <si>
-    <t>47,006,763.3</t>
-  </si>
-  <si>
-    <t>27,293,512.0</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>19,471,823.3</t>
+    <t>53,986,700.0</t>
+  </si>
+  <si>
+    <t>44,711,159.5</t>
+  </si>
+  <si>
+    <t>28,861,345.3</t>
+  </si>
+  <si>
+    <t>58,554,736.3</t>
+  </si>
+  <si>
+    <t>42,182,559.0</t>
+  </si>
+  <si>
+    <t>33,974,798.79</t>
+  </si>
+  <si>
+    <t>30,387,275.4</t>
+  </si>
+  <si>
+    <t>22,891,682.5</t>
+  </si>
+  <si>
+    <t>GMFIL</t>
+  </si>
+  <si>
+    <t>98,123,585.0</t>
+  </si>
+  <si>
+    <t>68,730,531.09</t>
+  </si>
+  <si>
+    <t>CBBL</t>
+  </si>
+  <si>
+    <t>68,396,933.2</t>
+  </si>
+  <si>
+    <t>47,545,450.9</t>
+  </si>
+  <si>
+    <t>19,664,580.7</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -506,103 +515,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>3,496,857,258.9</t>
-  </si>
-  <si>
-    <t>2,162,627,540.69</t>
-  </si>
-  <si>
-    <t>2,016,599,572.0</t>
-  </si>
-  <si>
-    <t>1,571,526,960.7</t>
-  </si>
-  <si>
-    <t>1,186,694,322.7</t>
+    <t>1,368,729,200.7</t>
+  </si>
+  <si>
+    <t>1,126,428,281.4</t>
+  </si>
+  <si>
+    <t>895,620,045.0</t>
+  </si>
+  <si>
+    <t>799,090,140.7</t>
+  </si>
+  <si>
+    <t>541,777,551.2</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>6,267,601,813.1</t>
+    <t>6,796,056,778.3</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>5,701,394,239.0</t>
+    <t>2,990,304,059.0</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>2,781,622,346.2</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>5,296,867,428.7</t>
+    <t>2,378,179,805.69</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>1,380,812,623.1</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>1,355,738,331.5</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>1,225,936,453.09</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>2,401,186,924.19</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>1,844,411,707.2</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>1,701,279,145.7</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>1,099,890,172.59</t>
+    <t>1,148,252,882.2</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>894,233,803.6</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>641,202,657.2</t>
+    <t>852,111,068.7</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>350,176,371.7</t>
+    <t>821,496,372.8</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>322,058,934.39</t>
+    <t>464,422,418.3</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>254,611,001.8</t>
+    <t>357,765,228.8</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>25,218,272.0</t>
+    <t>29,029,219.0</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>15,615,566.33</t>
+    <t>28,473,177.33</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -620,214 +629,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>3,410,054,314.3</t>
-  </si>
-  <si>
-    <t>982,221,109.1</t>
-  </si>
-  <si>
-    <t>664,896,544.1</t>
-  </si>
-  <si>
-    <t>82,281,105.2</t>
-  </si>
-  <si>
-    <t>37,757,833.79</t>
-  </si>
-  <si>
-    <t>520,680,517.9</t>
-  </si>
-  <si>
-    <t>512,982,962.2</t>
-  </si>
-  <si>
-    <t>230,940,807.9</t>
-  </si>
-  <si>
-    <t>104,930,455.6</t>
-  </si>
-  <si>
-    <t>74,278,924.2</t>
-  </si>
-  <si>
-    <t>175,623,647.7</t>
-  </si>
-  <si>
-    <t>65,068,999.1</t>
-  </si>
-  <si>
-    <t>23,052,570.3</t>
-  </si>
-  <si>
-    <t>18,066,351.5</t>
-  </si>
-  <si>
-    <t>16,018,707.3</t>
-  </si>
-  <si>
-    <t>2,125,252,920.0</t>
-  </si>
-  <si>
-    <t>84,675,010.0</t>
-  </si>
-  <si>
-    <t>82,004,787.0</t>
-  </si>
-  <si>
-    <t>51,956,252.9</t>
-  </si>
-  <si>
-    <t>44,940,791.0</t>
-  </si>
-  <si>
-    <t>311,558,662.0</t>
-  </si>
-  <si>
-    <t>211,451,875.3</t>
-  </si>
-  <si>
-    <t>85,580,082.3</t>
-  </si>
-  <si>
-    <t>26,317,014.2</t>
-  </si>
-  <si>
-    <t>23,028,694.8</t>
-  </si>
-  <si>
-    <t>1,015,910,741.7</t>
-  </si>
-  <si>
-    <t>169,497,796.1</t>
-  </si>
-  <si>
-    <t>140,983,143.9</t>
-  </si>
-  <si>
-    <t>67,748,776.5</t>
-  </si>
-  <si>
-    <t>22,852,118.1</t>
-  </si>
-  <si>
-    <t>121,588,285.2</t>
-  </si>
-  <si>
-    <t>57,077,149.4</t>
-  </si>
-  <si>
-    <t>53,446,737.7</t>
-  </si>
-  <si>
-    <t>11,809,718.3</t>
-  </si>
-  <si>
-    <t>10,192,833.19</t>
-  </si>
-  <si>
-    <t>52,126,761.0</t>
-  </si>
-  <si>
-    <t>50,778,634.3</t>
-  </si>
-  <si>
-    <t>47,028,430.5</t>
-  </si>
-  <si>
-    <t>28,448,701.3</t>
-  </si>
-  <si>
-    <t>19,160,311.5</t>
-  </si>
-  <si>
-    <t>797,279,899.3</t>
-  </si>
-  <si>
-    <t>286,808,544.7</t>
-  </si>
-  <si>
-    <t>89,777,759.2</t>
-  </si>
-  <si>
-    <t>85,390,742.0</t>
-  </si>
-  <si>
-    <t>75,864,367.8</t>
-  </si>
-  <si>
-    <t>2,148,744,893.5</t>
-  </si>
-  <si>
-    <t>88,509,950.8</t>
-  </si>
-  <si>
-    <t>67,133,251.09</t>
-  </si>
-  <si>
-    <t>52,560,140.1</t>
-  </si>
-  <si>
-    <t>14,604,059.1</t>
-  </si>
-  <si>
-    <t>58,813,229.9</t>
-  </si>
-  <si>
-    <t>30,543,056.2</t>
-  </si>
-  <si>
-    <t>29,655,166.5</t>
-  </si>
-  <si>
-    <t>17,815,162.2</t>
-  </si>
-  <si>
-    <t>14,966,677.1</t>
-  </si>
-  <si>
-    <t>409,558,568.8</t>
-  </si>
-  <si>
-    <t>258,289,280.8</t>
-  </si>
-  <si>
-    <t>151,436,793.1</t>
-  </si>
-  <si>
-    <t>48,068,847.8</t>
-  </si>
-  <si>
-    <t>27,535,341.3</t>
-  </si>
-  <si>
-    <t>79,675,628.4</t>
-  </si>
-  <si>
-    <t>40,465,624.5</t>
-  </si>
-  <si>
-    <t>36,036,535.1</t>
-  </si>
-  <si>
-    <t>35,947,890.0</t>
-  </si>
-  <si>
-    <t>9,481,202.3</t>
-  </si>
-  <si>
-    <t>1,098,071,981.8</t>
-  </si>
-  <si>
-    <t>70,229,880.8</t>
-  </si>
-  <si>
-    <t>69,436,857.7</t>
-  </si>
-  <si>
-    <t>18,624,403.2</t>
-  </si>
-  <si>
-    <t>15,384,277.9</t>
+    <t>441,721,763.4</t>
+  </si>
+  <si>
+    <t>366,563,360.1</t>
+  </si>
+  <si>
+    <t>202,356,895.3</t>
+  </si>
+  <si>
+    <t>121,799,359.5</t>
+  </si>
+  <si>
+    <t>72,749,143.3</t>
+  </si>
+  <si>
+    <t>760,936,395.0</t>
+  </si>
+  <si>
+    <t>355,921,095.8</t>
+  </si>
+  <si>
+    <t>145,165,289.0</t>
+  </si>
+  <si>
+    <t>88,597,716.8</t>
+  </si>
+  <si>
+    <t>31,370,266.2</t>
+  </si>
+  <si>
+    <t>228,181,588.8</t>
+  </si>
+  <si>
+    <t>105,232,961.2</t>
+  </si>
+  <si>
+    <t>63,244,361.6</t>
+  </si>
+  <si>
+    <t>39,432,765.2</t>
+  </si>
+  <si>
+    <t>36,596,056.4</t>
+  </si>
+  <si>
+    <t>206,061,393.7</t>
+  </si>
+  <si>
+    <t>169,207,739.3</t>
+  </si>
+  <si>
+    <t>92,537,004.0</t>
+  </si>
+  <si>
+    <t>75,046,726.3</t>
+  </si>
+  <si>
+    <t>37,468,223.29</t>
+  </si>
+  <si>
+    <t>252,946,264.3</t>
+  </si>
+  <si>
+    <t>110,150,539.9</t>
+  </si>
+  <si>
+    <t>77,206,885.09</t>
+  </si>
+  <si>
+    <t>47,171,786.3</t>
+  </si>
+  <si>
+    <t>40,111,768.2</t>
+  </si>
+  <si>
+    <t>195,285,915.8</t>
+  </si>
+  <si>
+    <t>174,332,069.8</t>
+  </si>
+  <si>
+    <t>82,717,990.0</t>
+  </si>
+  <si>
+    <t>37,981,744.29</t>
+  </si>
+  <si>
+    <t>26,601,522.1</t>
+  </si>
+  <si>
+    <t>131,423,033.9</t>
+  </si>
+  <si>
+    <t>129,060,707.0</t>
+  </si>
+  <si>
+    <t>114,765,212.9</t>
+  </si>
+  <si>
+    <t>29,416,611.1</t>
+  </si>
+  <si>
+    <t>21,503,526.7</t>
+  </si>
+  <si>
+    <t>719,059,433.7</t>
+  </si>
+  <si>
+    <t>496,870,181.6</t>
+  </si>
+  <si>
+    <t>146,222,505.19</t>
+  </si>
+  <si>
+    <t>132,215,620.8</t>
+  </si>
+  <si>
+    <t>96,659,578.8</t>
+  </si>
+  <si>
+    <t>178,301,522.2</t>
+  </si>
+  <si>
+    <t>175,684,354.6</t>
+  </si>
+  <si>
+    <t>127,099,613.5</t>
+  </si>
+  <si>
+    <t>40,498,551.9</t>
+  </si>
+  <si>
+    <t>34,274,325.7</t>
+  </si>
+  <si>
+    <t>337,236,466.3</t>
+  </si>
+  <si>
+    <t>162,818,270.29</t>
+  </si>
+  <si>
+    <t>91,679,157.3</t>
+  </si>
+  <si>
+    <t>88,077,793.9</t>
+  </si>
+  <si>
+    <t>66,163,320.9</t>
+  </si>
+  <si>
+    <t>243,949,502.5</t>
+  </si>
+  <si>
+    <t>218,050,268.3</t>
+  </si>
+  <si>
+    <t>78,209,540.0</t>
+  </si>
+  <si>
+    <t>76,349,466.8</t>
+  </si>
+  <si>
+    <t>40,260,769.79</t>
+  </si>
+  <si>
+    <t>289,057,365.0</t>
+  </si>
+  <si>
+    <t>134,344,282.0</t>
+  </si>
+  <si>
+    <t>102,736,778.6</t>
+  </si>
+  <si>
+    <t>64,322,925.5</t>
+  </si>
+  <si>
+    <t>50,509,775.3</t>
+  </si>
+  <si>
+    <t>244,409,635.7</t>
+  </si>
+  <si>
+    <t>97,112,391.4</t>
+  </si>
+  <si>
+    <t>44,535,847.0</t>
+  </si>
+  <si>
+    <t>36,980,752.9</t>
+  </si>
+  <si>
+    <t>33,329,243.7</t>
+  </si>
+  <si>
+    <t>244,908,588.8</t>
+  </si>
+  <si>
+    <t>140,071,908.1</t>
+  </si>
+  <si>
+    <t>84,398,682.7</t>
+  </si>
+  <si>
+    <t>76,338,321.4</t>
+  </si>
+  <si>
+    <t>25,515,643.8</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1645,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.6175399819892111</v>
+        <v>0.1023139571739554</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1645,52 +1654,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.08554306234593601</v>
+        <v>0.3462182711973399</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="J9" s="14">
-        <v>0.02967751564943882</v>
+        <v>0.0432126385258972</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.7931333541141879</v>
+        <v>0.09196105413895747</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1401256400680931</v>
+        <v>0.1387719501624613</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="S9" s="16">
-        <v>0.6035874454798661</v>
+        <v>0.1290254568719283</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V9" s="18">
-        <v>0.04893781629202069</v>
+        <v>0.06511956649643491</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1702,7 +1711,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1519325021258728</v>
+        <v>0.03620900074231549</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1711,52 +1720,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.03568934846653302</v>
+        <v>0.07127550663916637</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.01187363380534346</v>
+        <v>0.03214155541310641</v>
       </c>
       <c r="K10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="M10" s="16">
-        <v>0.02684628529842051</v>
+        <v>0.0610677938396451</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="O10" s="17" t="s">
         <v>93</v>
       </c>
       <c r="P10" s="18">
-        <v>0.03197364602883516</v>
+        <v>0.02149327743733046</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S10" s="16">
-        <v>0.07550585872132401</v>
+        <v>0.04610339346829456</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V10" s="18">
-        <v>0.01933824487349978</v>
+        <v>0.04096031106648936</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1768,61 +1777,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.1128254151847586</v>
+        <v>0.02404686103323645</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.02731027009754767</v>
+        <v>0.06268433222499861</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.003586570496228815</v>
+        <v>0.02407685640794548</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.01481693950053143</v>
+        <v>0.02495945023600551</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P11" s="18">
-        <v>0.03070881787851386</v>
+        <v>0.02145383440147952</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S11" s="16">
-        <v>0.06758054641342537</v>
+        <v>0.01804673126710525</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01419145824751179</v>
+        <v>0.01248115558858297</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1834,61 +1843,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.007811050148935019</v>
+        <v>0.0237764529075527</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.02231645186459343</v>
+        <v>0.03163704068370141</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.00340863428259668</v>
+        <v>0.01156108539221119</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.009620743808748944</v>
+        <v>0.02074060696592846</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01724885321247712</v>
+        <v>0.01709932081063924</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01459574457510886</v>
+        <v>0.01415754094923794</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V12" s="18">
-        <v>0.006803406880902955</v>
+        <v>0.01104545877314506</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1900,61 +1909,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.005365943529323904</v>
+        <v>0.02015508473736348</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.02209199201501888</v>
+        <v>0.009671644280705178</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13" s="14">
-        <v>0.003387942310396536</v>
+        <v>0.01060011246894002</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M13" s="16">
-        <v>0.007266195090397538</v>
+        <v>0.01962714754692223</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="P13" s="18">
-        <v>0.012287148768719</v>
+        <v>0.01483867107618979</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0117448931265837</v>
+        <v>0.01181012993475338</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="V13" s="18">
-        <v>0.004593144032256394</v>
+        <v>0.01050597747958912</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1965,7 +1974,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1974,7 +1983,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1983,7 +1992,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1992,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2001,7 +2010,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2010,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2019,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2028,552 +2037,552 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D16" s="10">
-        <v>0.004777841619710658</v>
+        <v>0.2125947086782068</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2086248365834335</v>
+        <v>0.04129956082896916</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J16" s="14">
-        <v>0.7773941954703372</v>
+        <v>0.08324689925870357</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="M16" s="16">
-        <v>0.00450699875109689</v>
+        <v>0.07983504251988136</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="P16" s="18">
-        <v>0.10534637966827</v>
+        <v>0.2090326273633212</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="S16" s="16">
-        <v>0.01270003503505571</v>
+        <v>0.04809237158533332</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="V16" s="18">
-        <v>0.5258843121986101</v>
+        <v>0.08396286145870782</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D17" s="10">
-        <v>0.004381498766339319</v>
+        <v>0.03963649580078426</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G17" s="12">
-        <v>0.0191685529582644</v>
+        <v>0.03455679584107086</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J17" s="14">
-        <v>0.01251955707713162</v>
+        <v>0.06052582705991191</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="M17" s="16">
-        <v>0.003797918151650495</v>
+        <v>0.07910675605506615</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="P17" s="18">
-        <v>0.08831195899909766</v>
+        <v>0.09222235719785711</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="S17" s="16">
-        <v>0.009410076499956921</v>
+        <v>0.03464552024373554</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="V17" s="18">
-        <v>0.07898578725274734</v>
+        <v>0.05881167163564916</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D18" s="10">
-        <v>0.002108251450360197</v>
+        <v>0.03678103047921426</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G18" s="12">
-        <v>0.0174756152780183</v>
+        <v>0.02614870477579052</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J18" s="14">
-        <v>0.005947731204253041</v>
+        <v>0.05596500700258659</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="M18" s="16">
-        <v>0.00371257403652121</v>
+        <v>0.0417504520827218</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05704870335029254</v>
+        <v>0.03909048316201269</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="S18" s="16">
-        <v>0.006458073484359287</v>
+        <v>0.02790429522310967</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02931305637910778</v>
+        <v>0.05852621697904835</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D19" s="10">
-        <v>0.001711678476647647</v>
+        <v>0.03420473920282556</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.01281447650949128</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.03932776249935701</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.02979165857715259</v>
+      </c>
+      <c r="N19" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="G19" s="12">
-        <v>0.01573832669054103</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="J19" s="14">
-        <v>0.004514452491685013</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="M19" s="16">
-        <v>0.002898494354351013</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>54</v>
-      </c>
       <c r="O19" s="17" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02774416168342194</v>
+        <v>0.03237428528857688</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="S19" s="16">
-        <v>0.00574140262221171</v>
+        <v>0.02495777852222448</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01702002435125873</v>
+        <v>0.04068392025126778</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D20" s="10">
-        <v>0.001667824182148994</v>
+        <v>0.01988827579126735</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01443317448273397</v>
+        <v>0.01020485817582293</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J20" s="14">
-        <v>0.00451067024790928</v>
+        <v>0.03686363449816456</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M20" s="16">
-        <v>0.00286747581830316</v>
+        <v>0.02664777917327038</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01948245241893161</v>
+        <v>0.02089781247015809</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="S20" s="16">
-        <v>0.004891430619963682</v>
+        <v>0.0188014731270077</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01214247938225784</v>
+        <v>0.01682668305441225</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2674966435039364</v>
+        <v>0.2900507134096747</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2433313199695519</v>
+        <v>0.1276239816586342</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D33" s="22">
-        <v>0.2260664127228226</v>
+        <v>0.1187175993772999</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1024808948945259</v>
+        <v>0.1014989679695282</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07871813743562291</v>
+        <v>0.05893206891591388</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D36" s="22">
-        <v>0.07260934480343215</v>
+        <v>0.05786191656079458</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04694250499106666</v>
+        <v>0.05232206769548631</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D38" s="22">
-        <v>0.03816524216180957</v>
+        <v>0.04900658992730434</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02736605861723854</v>
+        <v>0.03636747476417347</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01494527043315894</v>
+        <v>0.03506086202147703</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D41" s="22">
-        <v>0.0137452388539412</v>
+        <v>0.01982120781884601</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D42" s="22">
-        <v>0.0108666106130613</v>
+        <v>0.01526915728219873</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001076297332876158</v>
+        <v>0.001238945752713663</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0006664609055025551</v>
+        <v>0.001215214302502125</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D45" s="22">
         <v>7.366906475406133E-05</v>
@@ -2581,13 +2590,13 @@
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2966,331 +2975,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D9" s="10">
-        <v>0.6212674074560713</v>
+        <v>0.134381103073098</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1657278653952166</v>
+        <v>0.3524164870079368</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J9" s="14">
-        <v>0.06379243120275888</v>
+        <v>0.1518851153736631</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M9" s="16">
-        <v>0.7936423398391472</v>
+        <v>0.1480605435592334</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1776531543371343</v>
+        <v>0.1831523631841391</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="S9" s="16">
-        <v>0.6052745063119042</v>
+        <v>0.1603928806017988</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="V9" s="18">
-        <v>0.07582152032804686</v>
+        <v>0.1124566941559337</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1789478717216407</v>
+        <v>0.111516327149615</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1632778035414201</v>
+        <v>0.1648396147931015</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02363525472156065</v>
+        <v>0.07004649471076961</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M10" s="16">
-        <v>0.03162055321975663</v>
+        <v>0.1215802213376326</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1205714917261629</v>
+        <v>0.07975738145223836</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1009859337481826</v>
+        <v>0.1431829978211663</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="V10" s="18">
-        <v>0.03559287176704971</v>
+        <v>0.1104352869048138</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D11" s="10">
-        <v>0.1211354758917684</v>
+        <v>0.06156124750465804</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G11" s="12">
-        <v>0.07350635526037562</v>
+        <v>0.06723116612771807</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J11" s="14">
-        <v>0.008373470908778491</v>
+        <v>0.04209751193716671</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M11" s="16">
-        <v>0.03062340035871631</v>
+        <v>0.06649027683239897</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="P11" s="18">
-        <v>0.04879842361444778</v>
+        <v>0.05590366593981477</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="S11" s="16">
-        <v>0.08399704749609957</v>
+        <v>0.06793821581725552</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="V11" s="18">
-        <v>0.03332897492815647</v>
+        <v>0.09820284971244995</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01499054390302802</v>
+        <v>0.0370539412801928</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G12" s="12">
-        <v>0.0333984080903818</v>
+        <v>0.04103272798717961</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J12" s="14">
-        <v>0.006562308095987746</v>
+        <v>0.02624773595188748</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01940224701388975</v>
+        <v>0.05392305122664524</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01500616466688111</v>
+        <v>0.03415596652661138</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04036438002481752</v>
+        <v>0.03119529308399798</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="V12" s="18">
-        <v>0.007364449582285556</v>
+        <v>0.02517134736132997</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D13" s="10">
-        <v>0.006878984718135936</v>
+        <v>0.02213182807437121</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02364230488432318</v>
+        <v>0.01452867688199855</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J13" s="14">
-        <v>0.005818534672152703</v>
+        <v>0.02435952995930353</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01678243289907447</v>
+        <v>0.02692190617750215</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01313113955883904</v>
+        <v>0.02904397563512228</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01361517693770324</v>
+        <v>0.02184845097780171</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="V13" s="18">
-        <v>0.00635617245857984</v>
+        <v>0.01840024121811005</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3301,7 +3310,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3310,7 +3319,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3319,7 +3328,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3328,7 +3337,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3337,7 +3346,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3346,7 +3355,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3355,7 +3364,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3364,331 +3373,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D16" s="10">
-        <v>0.009496815792566053</v>
+        <v>0.2187530882154474</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2537669286464044</v>
+        <v>0.08257772462295176</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J16" s="14">
-        <v>0.7804966050188593</v>
+        <v>0.2244756023549168</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M16" s="16">
-        <v>0.02196287743076419</v>
+        <v>0.1752841485374975</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2335334577637974</v>
+        <v>0.209299550803962</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="S16" s="16">
-        <v>0.04747033835295526</v>
+        <v>0.2007393382987594</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="V16" s="18">
-        <v>0.6847492499195753</v>
+        <v>0.2095645599522484</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D17" s="10">
-        <v>0.009251204695898452</v>
+        <v>0.1511584183074882</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G17" s="12">
-        <v>0.09128854692306426</v>
+        <v>0.08136562198524971</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J17" s="14">
-        <v>0.03214979885176689</v>
+        <v>0.1083771565423325</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M17" s="16">
-        <v>0.01140582485985083</v>
+        <v>0.1566748660097735</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1472785419318235</v>
+        <v>0.09727549365739496</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="S17" s="16">
-        <v>0.02410921539313063</v>
+        <v>0.07976067365107625</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="V17" s="18">
-        <v>0.04379481399835967</v>
+        <v>0.1198574044564021</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D18" s="10">
-        <v>0.008567966489841851</v>
+        <v>0.04448397876446539</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02857544286886361</v>
+        <v>0.05886431452623125</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02438506065840179</v>
+        <v>0.06102464031870525</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01107425638986041</v>
+        <v>0.05619561624811822</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="P18" s="18">
-        <v>0.08635042853315045</v>
+        <v>0.07438925353805151</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02147038622245932</v>
+        <v>0.03657833060366036</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04330029088703891</v>
+        <v>0.07221867100389312</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D19" s="10">
-        <v>0.005182982226419832</v>
+        <v>0.04022278827703882</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02717909526027547</v>
+        <v>0.01875630799537011</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01909161531062208</v>
+        <v>0.05862745525926155</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M19" s="16">
-        <v>0.006652792653507766</v>
+        <v>0.05485910461871073</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02740922811198111</v>
+        <v>0.04657469777165758</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02141757191807497</v>
+        <v>0.03037315548413106</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01161403471974075</v>
+        <v>0.06532154225407186</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D20" s="10">
-        <v>0.003490758784028131</v>
+        <v>0.02940588827171434</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G20" s="12">
-        <v>0.0241469371386511</v>
+        <v>0.01587364927887283</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J20" s="14">
-        <v>0.005304686741327573</v>
+        <v>0.04404046654793558</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M20" s="16">
-        <v>0.005589070609657594</v>
+        <v>0.0289284244547996</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01570086418491093</v>
+        <v>0.03657292482929489</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="S20" s="16">
-        <v>0.005648852606650011</v>
+        <v>0.0273740857522832</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="V20" s="18">
-        <v>0.009593517480803915</v>
+        <v>0.02183334888762103</v>
       </c>
     </row>
   </sheetData>
